--- a/docs/verification/files/rocscience/joints/rj015.xlsx
+++ b/docs/verification/files/rocscience/joints/rj015.xlsx
@@ -14351,20 +14351,10 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
-        <v>-23.83505</v>
-      </c>
-      <c r="C3" s="3">
-        <v>80.0</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="E3" s="3">
-        <v>-3.4752035547</v>
-      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
